--- a/Sajjad data/by_country_and_state/Canada/AB.xlsx
+++ b/Sajjad data/by_country_and_state/Canada/AB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="308">
   <si>
     <t>Business Name</t>
   </si>
@@ -848,6 +848,93 @@
   </si>
   <si>
     <t>2026-10-25T09:48:51.028Z</t>
+  </si>
+  <si>
+    <t>Pope A James D Dr</t>
+  </si>
+  <si>
+    <t>+1 780-831-0135</t>
+  </si>
+  <si>
+    <t>10140 107 Ave, Grande Prairie, AB T8V 2W8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pope+A+James+D+Dr/data=!4m7!3m6!1s0x5390915212b7cd39:0x5ba40a1bc01544a!8m2!3d55.1771126!4d-118.8010891!16s%2Fg%2F1trqgx3l!19sChIJOc23ElKRkFMRSlQBvKFAugU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:09.773Z</t>
+  </si>
+  <si>
+    <t>Dr Cele's Office at O &amp; C Medical Clinic</t>
+  </si>
+  <si>
+    <t>+1 587-752-6500</t>
+  </si>
+  <si>
+    <t>Family practice physician</t>
+  </si>
+  <si>
+    <t>9719 98 Ave #111, Grande Prairie, AB T8V 8K6, Canada</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Cele%27s+Office+at+O+%26+C+Medical+Clinic/data=!4m7!3m6!1s0x539091355c92354f:0x247064e063176db3!8m2!3d55.168614!4d-118.7855466!16s%2Fg%2F11bv2lhtqh!19sChIJTzWSXDWRkFMRs20XY-BkcCQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:13.951Z</t>
+  </si>
+  <si>
+    <t>Deans Family Dental Hygiene</t>
+  </si>
+  <si>
+    <t>+1 587-775-3326</t>
+  </si>
+  <si>
+    <t>218 Main St N, Airdrie, AB T4B 0R6, Canada</t>
+  </si>
+  <si>
+    <t>Airdrie</t>
+  </si>
+  <si>
+    <t>Sunday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Deans+Family+Dental+Hygiene/data=!4m7!3m6!1s0x53715f6b0770d57b:0x56516f6df464bf2c!8m2!3d51.2932953!4d-114.0129768!16s%2Fg%2F11j7fbnf1z!19sChIJe9VwB2tfcVMRLL9k9G1vUVY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:28.513Z</t>
+  </si>
+  <si>
+    <t>Bell R Scott Dr</t>
+  </si>
+  <si>
+    <t>+1 403-948-6898</t>
+  </si>
+  <si>
+    <t>44 Gateway Dr NE #107, Airdrie, AB T4B 0J6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bell+R+Scott+Dr/data=!4m7!3m6!1s0x53715f79435596bb:0x1d3c47d0556b2686!8m2!3d51.3043599!4d-114.0105971!16s%2Fg%2F1tdgv1mm!19sChIJu5ZVQ3lfcVMRhiZrVdBHPB0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:03.035Z</t>
+  </si>
+  <si>
+    <t>Rocky View Dental Repair</t>
+  </si>
+  <si>
+    <t>+1 587-351-8324</t>
+  </si>
+  <si>
+    <t>203 304 Main St S Ste 432, Airdrie, AB T4B 3C3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rocky+View+Dental+Repair/data=!4m7!3m6!1s0x53715f6e309d6d9d:0xe596e03a86f6f66a!8m2!3d51.2892951!4d-114.0126675!16s%2Fg%2F11jk2h_861!19sChIJnW2dMG5fcVMRavb2hjrgluU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:18.557Z</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3049,6 +3136,211 @@
         <v>278</v>
       </c>
     </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>279</v>
+      </c>
+      <c r="B45" t="s">
+        <v>280</v>
+      </c>
+      <c r="C45" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" t="s">
+        <v>281</v>
+      </c>
+      <c r="E45" t="s">
+        <v>264</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>282</v>
+      </c>
+      <c r="M45" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>284</v>
+      </c>
+      <c r="B46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" t="s">
+        <v>286</v>
+      </c>
+      <c r="D46" t="s">
+        <v>287</v>
+      </c>
+      <c r="E46" t="s">
+        <v>264</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>288</v>
+      </c>
+      <c r="I46" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>289</v>
+      </c>
+      <c r="M46" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>293</v>
+      </c>
+      <c r="E47" t="s">
+        <v>294</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" t="s">
+        <v>295</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>296</v>
+      </c>
+      <c r="M47" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" t="s">
+        <v>294</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>301</v>
+      </c>
+      <c r="M48" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B49" t="s">
+        <v>304</v>
+      </c>
+      <c r="C49" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" t="s">
+        <v>305</v>
+      </c>
+      <c r="E49" t="s">
+        <v>294</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>306</v>
+      </c>
+      <c r="M49" t="s">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
